--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136373228</v>
       </c>
       <c r="B2" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28733-2026 artfynd.xlsx
+++ b/artfynd/A 28733-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136373218</v>
       </c>
       <c r="B3" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
